--- a/output/laminas_provinciales/prov_i_peringrmin_a_2022_metropolitana.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2022_metropolitana.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -408,7 +408,7 @@
         <v>4.86</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -426,7 +426,7 @@
         <v>3.15</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -444,7 +444,7 @@
         <v>3.88</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -462,7 +462,7 @@
         <v>4.73</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -480,7 +480,7 @@
         <v>3.2</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -498,7 +498,7 @@
         <v>3.9</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         <v>4.86</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -534,7 +534,7 @@
         <v>3.38</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -552,13 +552,13 @@
         <v>4.03</v>
       </c>
       <c r="G10">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Maipo</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -567,16 +567,25 @@
         </is>
       </c>
       <c r="C11">
-        <v>5.28</v>
+        <v>4.86</v>
+      </c>
+      <c r="D11">
+        <v>5.32</v>
+      </c>
+      <c r="E11">
+        <v>-0.46</v>
+      </c>
+      <c r="F11">
+        <v>-8.64661654135338</v>
       </c>
       <c r="G11">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Maipo</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -585,16 +594,25 @@
         </is>
       </c>
       <c r="C12">
-        <v>4.38</v>
+        <v>3.45</v>
+      </c>
+      <c r="D12">
+        <v>3.78</v>
+      </c>
+      <c r="E12">
+        <v>-0.3299999999999996</v>
+      </c>
+      <c r="F12">
+        <v>-8.73015873015872</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Maipo</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -603,16 +621,25 @@
         </is>
       </c>
       <c r="C13">
-        <v>4.76</v>
+        <v>4.08</v>
+      </c>
+      <c r="D13">
+        <v>4.46</v>
+      </c>
+      <c r="E13">
+        <v>-0.3799999999999999</v>
+      </c>
+      <c r="F13">
+        <v>-8.520179372197312</v>
       </c>
       <c r="G13">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Talagante</t>
+          <t>Maipo</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -621,16 +648,16 @@
         </is>
       </c>
       <c r="C14">
-        <v>5.59</v>
+        <v>5.28</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Talagante</t>
+          <t>Maipo</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -639,16 +666,16 @@
         </is>
       </c>
       <c r="C15">
-        <v>4.6</v>
+        <v>4.38</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Talagante</t>
+          <t>Maipo</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -657,16 +684,16 @@
         </is>
       </c>
       <c r="C16">
-        <v>5.01</v>
+        <v>4.76</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Melipilla</t>
+          <t>Talagante</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -675,16 +702,16 @@
         </is>
       </c>
       <c r="C17">
-        <v>7.01</v>
+        <v>5.59</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Melipilla</t>
+          <t>Talagante</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -693,27 +720,81 @@
         </is>
       </c>
       <c r="C18">
-        <v>6.67</v>
+        <v>4.6</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>5.01</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Melipilla</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>7.01</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>6.67</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C19">
+      <c r="C22">
         <v>6.81</v>
       </c>
-      <c r="G19">
+      <c r="G22">
         <v>1</v>
       </c>
     </row>
@@ -806,7 +887,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1155,6 +1236,60 @@
         <v>0</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>4.08</v>
+      </c>
+      <c r="D20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>3.14</v>
+      </c>
+      <c r="D21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>3.83</v>
+      </c>
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2022_metropolitana.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2022_metropolitana.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t xml:space="preserve">Provincia</t>
   </si>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:20</t>
+    <t xml:space="preserve">2026-08-19 13:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -92,13 +92,19 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">prov_i_peringrmin_a_2022_metropolitana.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">% con ingreso igual al mínimo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region de Metropolitana</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
@@ -941,23 +947,23 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -980,7 +986,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2">
@@ -1053,10 +1059,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2">
@@ -1064,7 +1070,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>3.88</v>
@@ -1075,7 +1081,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>2.9</v>
@@ -1086,7 +1092,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>3.56</v>
@@ -1097,7 +1103,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>4.03</v>
@@ -1108,7 +1114,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>3.17</v>
@@ -1119,7 +1125,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>3.82</v>
@@ -1130,7 +1136,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>4.76</v>
@@ -1141,7 +1147,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>3.59</v>
@@ -1152,7 +1158,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>4.37</v>
@@ -1163,7 +1169,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>6.81</v>
@@ -1174,7 +1180,7 @@
         <v>16</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>4.86</v>
@@ -1185,7 +1191,7 @@
         <v>16</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>6.04</v>
@@ -1196,7 +1202,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>3.9</v>
@@ -1207,7 +1213,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>3.03</v>
@@ -1218,7 +1224,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>3.69</v>
@@ -1229,7 +1235,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>5.01</v>
@@ -1240,7 +1246,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>3.66</v>
@@ -1251,7 +1257,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>4.53</v>
@@ -1262,7 +1268,7 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>4.08</v>
@@ -1273,7 +1279,7 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>3.14</v>
@@ -1284,7 +1290,7 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>3.83</v>

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2022_metropolitana.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2022_metropolitana.xlsx
@@ -80,7 +80,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 13:51</t>
+    <t xml:space="preserve">2026-09-07 11:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
